--- a/data_extactor/batch_10_fa/batch_0026_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0026_fa.xlsx
@@ -503,32 +503,32 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Adobe Acrobat | Adobe Dreamweaver | Adobe InDesign | Adobe Photoshop | پایگاه‌های داده آرشیوی | ArchiveGrid | Archives Wiki | نرم‌افزار ویرایش صوتی | Corel WordPerfect Office Suite | سیستم‌های مدیریت پایگاه داده | مجموعه‌های تصاویر دیجیتال | نرم‌افزار نقشه‌برداری دیجیتال | نرم‌افزار ESRI ArcGIS | نرم‌افزار ایمیل | زبان نشانه‌گذاری توسعه‌پذیر XML | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | سیستم‌های سیستم اطلاعات جغرافیایی GIS | Google Books NGram Viewer | Gutenberg-e | IBM SPSS Statistics | مجموعه‌های دیجیتال کتابخانه کنگره | LinkedIn | Microsoft Access | Microsoft Active Server Pages ASP | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft SharePoint | Microsoft Word | پایگاه‌های داده آنلاین آرشیو ملی | National Union Catalog of Manuscript Collections (NUCMC) | نشانگرهای صفحه | ProQuest Archive Finder | QuarkXPress | نرم‌افزار مدیریت منابع | سیستم مدیریت پایگاه داده رابطه‌ای RDMS | نرم‌افزار اسکن | کاتالوگ‌های آنلاین قابل جستجو | آرشیوهای دیجیتال موسسه اسمیتسونین | نرم‌افزار تحلیل آماری | زبان پرس‌وجوی ساختاریافته SQL | نرم‌افزار کنترل نظارتی و جمع‌آوری داده SCADA | نرم‌افزار داده‌کاوی متن | TokenX | Web Scrapbook | نرم‌افزار مرورگر وب | نرم‌افزار Wonderware</t>
+          <t>Adobe Acrobat | Adobe Dreamweaver | Adobe InDesign | Adobe Photoshop | پایگاه‌های داده آرشیوی | ArchiveGrid | Archives Wiki | نرم‌افزار ویرایش صوتی | Corel WordPerfect Office Suite | سیستم‌های مدیریت پایگاه داده | مجموعه‌های تصاویر دیجیتال | نرم‌افزار نقشه‌برداری دیجیتال | نرم‌افزار ESRI ArcGIS | نرم‌افزار ایمیل | زبان نشانه‌گذاری توسعه‌پذیر XML | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | سیستم‌های سیستم اطلاعات جغرافیایی GIS | Google Books NGram Viewer | Gutenberg-e | IBM SPSS Statistics | مجموعه‌های دیجیتال کتابخانه کنگره | LinkedIn | Microsoft Access | Microsoft Active Server Pages ASP | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft SharePoint | Microsoft Word | پایگاه‌های داده آنلاین آرشیو ملی | National Union Catalog of Manuscript Collections (NUCMC) | نشانگرهای صفحه | ProQuest Archive Finder | QuarkXPress | نرم‌افزار مدیریت منابع | سیستم مدیریت پایگاه داده رابطه‌ای RDMS | نرم‌افزار اسکن | کاتالوگ‌های آنلاین قابل جستجو | آرشیوهای دیجیتال موسسه اسمیتسونین | نرم‌افزار تحلیل آماری | زبان پرس‌وجوی ساختاریافته SQL | نرم‌افزار کنترل نظارتی و گردآوری داده SCADA | نرم‌افزار داده‌کاوی متن | TokenX | Web Scrapbook | نرم‌افزار مرورگر وب | نرم‌افزار Wonderware</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>درک مطلب | نوشتن | تفکر انتقادی | گوش دادن فعال | یادگیری فعال | صحبت کردن | راهبردهای یادگیری | نظارت</t>
+          <t>درک مطلب | نگارش | تفکر انتقادی | گوش دادن فعال | یادگیری فعال | سخن گفتن | راهبردهای یادگیری | نظارت</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>تاریخ و باستان‌شناسی | زبان انگلیسی | جامعه‌شناسی و مردم‌شناسی | جغرافیا | اداری | آموزش و پرورش | ارتباطات و رسانه</t>
+          <t>تاریخ و باستان‌شناسی | زبان انگلیسی | جامعه‌شناسی و انسان‌شناسی | جغرافیا | اداری | آموزش و پرورش | ارتباطات و رسانه</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک نوشتاری | بیان نوشتاری | درک شنیداری | بیان شفاهی | دید نزدیک | استدلال استقرایی | وضوح گفتار | استدلال قیاسی | تشخیص گفتار | نظم‌دهی اطلاعات | روانی ایده‌ها | انعطاف‌پذیری دسته‌بندی | حساسیت به مسئله | توجه انتخابی</t>
+          <t>درک کتبی | بیان کتبی | درک شفاهی | بیان شفاهی | بینایی نزدیک | استدلال استقرایی | وضوح گفتار | استدلال قیاسی | تشخیص گفتار | ترتیب‌دهی اطلاعات | روانی ایده‌ها | انعطاف‌پذیری دسته‌بندی | حساسیت به مسئله | توجه انتخابی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>ایمیل | محیط داخلی، دارای تهویه مطبوع | کار با یا مشارکت در یک گروه کاری یا تیم | بحث‌های رودررو با افراد و درون تیم‌ها | تعیین وظایف، اولویت‌ها و اهداف | تعامل با مشتریان خارجی یا عموم مردم | اهمیت دقیق یا صحیح بودن | تماس با دیگران | آزادی در تصمیم‌گیری | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | تناوب تصمیم‌گیری | صرف زمان برای نشستن | تأثیر تصمیمات بر همکاران یا نتایج شرکت</t>
+          <t>ایمیل | محیط داخلی، دارای کنترل شرایط محیطی | کار با یا مشارکت در یک گروه کاری یا تیم | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | تعیین وظایف، اولویت‌ها و اهداف | تعامل با مشتریان خارجی یا عموم مردم | اهمیت دقیق یا درست بودن | ارتباط با دیگران | آزادی در تصمیم‌گیری | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | فراوانی تصمیم‌گیری | صرف زمان برای نشستن | تأثیر تصمیمات بر همکاران یا نتایج شرکت</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>مردم‌شناسان و باستان‌شناسان | مدرسان مردم‌شناسی و باستان‌شناسی، پس از متوسطه | مدرسان معماری، پس از متوسطه | آرشیوداران | مدرسان مطالعات منطقه‌ای، قومی و فرهنگی، پس از متوسطه | متصدیان موزه | ویراستاران | مدرسان زبان و ادبیات انگلیسی، پس از متوسطه | جغرافی‌دانان | مدرسان جغرافیا، پس از متوسطه | مدرسان تاریخ، پس از متوسطه | کتابداران و متخصصان مجموعه‌های رسانه‌ای | مدرسان علوم کتابداری، پس از متوسطه | تکنسین‌ها و مرمت‌گران موزه | تحلیلگران اخبار، گزارشگران و روزنامه‌نگاران | شاعران، ترانه‌سرایان و نویسندگان خلاق | دستیاران پژوهشی علوم اجتماعی | جامعه‌شناسان | مدرسان جامعه‌شناسی، پس از متوسطه | راهنمایان تور و همراهان</t>
+          <t>مردم‌شناسان و باستان‌شناسان | استادان انسان‌شناسی و باستان‌شناسی، پس از متوسطه | مدرسان معماری، پس از متوسطه | آرشیوچی‌ها | استادان مطالعات منطقه‌ای، قومی و فرهنگی، پس از متوسطه | موزه‌داران | ویراستاران | مدرسان زبان و ادبیات انگلیسی، آموزش عالی | جغرافیدانان | استادان جغرافیا، پس از متوسطه | مدرسان تاریخ، آموزش عالی | کتابداران و متخصصان مجموعه‌های رسانه‌ای | مدرسان علوم کتابداری، آموزش عالی | تکنسین‌ها و محافظان موزه | تحلیلگران اخبار، گزارشگران و روزنامه‌نگاران | شاعران، ترانه‌سرایان و نویسندگان خلاق | دستیاران تحقیقات علوم اجتماعی | جامعه‌شناسان | استادان جامعه‌شناسی، پس از متوسطه | راهنمایان تور و همراهان</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -560,32 +560,32 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Adobe Acrobat | Bare Bones Software BBEdit | CQ Press Political Reference Suite | نرم‌افزار تجسم داده‌ها | DataMystic TextPipe Pro | EBSCO Publishing Academic Search Premier | EBSCO Publishing Political Science Complete | نرم‌افزار ایمیل | Europa World Plus | FedStats | Gale Expanded Academic ASAP PLUS | IBM SPSS Statistics | IDM Computer Solutions UltraEdit | پایگاه داده Interuniversity Consortium for Political and Social Research (ICPSR) | پایگاه داده JSTOR | JudgeIt II | کاتالوگ آنلاین منابع الکترونیکی کتابخانه کنگره | Microsoft Access | Microsoft Active Server Pages ASP | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Publisher | Microsoft SharePoint | Microsoft Visio | Microsoft Word | Oxford Reference Online | پایگاه داده ProQuest Public Affairs Information Service (PAIS) | ProQuest Worldwide Political Science Abstracts | Python | R | نرم‌افزار SAP | SAS | Sage Reference Online | StataCorp Stata | زبان پرس‌وجوی ساختاریافته SQL | Tableau | WinBUGS</t>
+          <t>Adobe Acrobat | Bare Bones Software BBEdit | CQ Press Political Reference Suite | نرم‌افزار تجسم داده | DataMystic TextPipe Pro | EBSCO Publishing Academic Search Premier | EBSCO Publishing Political Science Complete | نرم‌افزار ایمیل | Europa World Plus | FedStats | Gale Expanded Academic ASAP PLUS | IBM SPSS Statistics | IDM Computer Solutions UltraEdit | پایگاه داده Interuniversity Consortium for Political and Social Research (ICPSR) | پایگاه داده JSTOR | JudgeIt II | کاتالوگ آنلاین منابع الکترونیکی کتابخانه کنگره | Microsoft Access | Microsoft Active Server Pages ASP | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Publisher | Microsoft SharePoint | Microsoft Visio | Microsoft Word | Oxford Reference Online | پایگاه داده ProQuest Public Affairs Information Service (PAIS) | ProQuest Worldwide Political Science Abstracts | Python | R | نرم‌افزار SAP | SAS | Sage Reference Online | StataCorp Stata | زبان پرس‌وجوی ساختاریافته SQL | Tableau | WinBUGS</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>درک مطلب | گوش دادن فعال | صحبت کردن | یادگیری فعال | تفکر انتقادی | نوشتن | راهبردهای یادگیری | ریاضیات</t>
+          <t>درک مطلب | گوش دادن فعال | سخن گفتن | یادگیری فعال | تفکر انتقادی | نگارش | راهبردهای یادگیری | ریاضیات</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>قانون و دولت | زبان انگلیسی | آموزش و پرورش | تاریخ و باستان‌شناسی | ریاضیات | ارتباطات و رسانه | جامعه‌شناسی و مردم‌شناسی | جغرافیا | فلسفه و الهیات | کامپیوتر و الکترونیک</t>
+          <t>قانون و دولت | زبان انگلیسی | آموزش و پرورش | تاریخ و باستان‌شناسی | ریاضیات | ارتباطات و رسانه | جامعه‌شناسی و انسان‌شناسی | جغرافیا | فلسفه و الهیات | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک نوشتاری | درک شنیداری | بیان شفاهی | بیان نوشتاری | استدلال استقرایی | وضوح گفتار | تشخیص گفتار | استدلال قیاسی | دید نزدیک | حساسیت به مسئله | نظم‌دهی اطلاعات | اصالت | روانی ایده‌ها | انعطاف‌پذیری دسته‌بندی | استدلال ریاضی</t>
+          <t>درک کتبی | درک شفاهی | بیان شفاهی | بیان کتبی | استدلال استقرایی | وضوح گفتار | تشخیص گفتار | استدلال قیاسی | بینایی نزدیک | حساسیت به مسئله | ترتیب‌دهی اطلاعات | اصالت | روانی ایده‌ها | انعطاف‌پذیری دسته‌بندی | استدلال ریاضی</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>ایمیل | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | محیط داخلی، دارای تهویه مطبوع | بحث‌های رودررو با افراد و درون تیم‌ها | سطح رقابت | سخنرانی عمومی | صرف زمان برای نشستن | تماس با دیگران | اهمیت دقیق یا صحیح بودن | مکالمات تلفنی | نامه‌ها و یادداشت‌های کتبی</t>
+          <t>ایمیل | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | محیط داخلی، دارای کنترل شرایط محیطی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | سطح رقابت | سخنرانی عمومی | صرف زمان برای نشستن | ارتباط با دیگران | اهمیت دقیق یا درست بودن | مکالمات تلفنی | نامه‌ها و یادداشت‌های کتبی</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>مدرسان کسب‌وکار، پس از متوسطه | مدیران ارشد اجرایی | تحلیلگران سیاست تغییرات اقلیمی | مدرسان عدالت کیفری و اجرای قانون، پس از متوسطه | مدرسان اقتصاد، پس از متوسطه | اقتصاددانان | اقتصاددانان محیط زیست | نمایندگان و مسئولان فرصت‌های برابر | مدرسان تاریخ، پس از متوسطه | تحلیلگران اطلاعاتی | متخصصان روابط کار | مدرسان حقوق، پس از متوسطه | قانون‌گذاران | تحلیلگران مدیریت | مدرسان علوم سیاسی، پس از متوسطه | مدیران روابط عمومی | جامعه‌شناسان | مدرسان جامعه‌شناسی، پس از متوسطه | پژوهشگران نظرسنجی | برنامه‌ریزان شهری و منطقه‌ای</t>
+          <t>اساتید کسب‌وکار، پس از متوسطه | مدیران ارشد اجرایی | تحلیل‌گران سیاست تغییرات اقلیمی | مدرسان عدالت کیفری و اجرای قانون، آموزش عالی | استادان اقتصاد، پس از متوسطه | اقتصاددانان | اقتصاددانان محیط‌زیست | نمایندگان و افسران فرصت‌های برابر | مدرسان تاریخ، آموزش عالی | تحلیلگران اطلاعاتی | متخصصان روابط کار | مدرسان حقوق، آموزش عالی | قانون‌گذاران | تحلیل‌گران مدیریت | استادان علوم سیاسی، پس از متوسطه | مدیران روابط عمومی | جامعه‌شناسان | استادان جامعه‌شناسی، پس از متوسطه | پژوهشگران نظرسنجی | برنامه‌ریزان شهری و منطقه‌ای</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>دانشمندان علوم اجتماعی و کارگران مرتبط، سایر</t>
+          <t>دانشمندان علوم اجتماعی و کارگران مرتبط، سایر (Social Scientists and Related Workers, All Other)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -622,27 +622,27 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | صحبت کردن | نوشتن | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
+          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>جامعه‌شناسی و مردم‌شناسی | زبان انگلیسی | ریاضیات | روان‌شناسی | تاریخ و باستان‌شناسی | جغرافیا | قانون و دولت | آموزش و پرورش | کامپیوتر و الکترونیک</t>
+          <t>جامعه‌شناسی و انسان‌شناسی | زبان انگلیسی | ریاضیات | روان‌شناسی | تاریخ و باستان‌شناسی | جغرافیا | قانون و دولت | آموزش و پرورش | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>درک شنیداری | درک نوشتاری | بیان شفاهی | بیان نوشتاری | استدلال قیاسی | استدلال استقرایی | نظم‌دهی اطلاعات | حساسیت به مسئله | دید نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | توجه انتخابی | اشتراک زمانی | تجسم | حفظ کردن | استدلال ریاضی | توانایی عددی | سرعت ادراکی | انعطاف‌پذیری بستار</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | توجه انتخابی | تقسیم توجه | تجسم | حفظ کردن | استدلال ریاضی | توانایی عددی | سرعت ادراکی | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | بحث‌های رودررو با افراد و درون تیم‌ها | محیط داخلی، دارای تهویه مطبوع | صرف زمان برای نشستن | تماس با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا صحیح بودن | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | تناوب تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعامل با مشتریان خارجی یا عموم مردم | سخنرانی عمومی</t>
+          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | صرف زمان برای نشستن | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | فراوانی تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعامل با مشتریان خارجی یا عموم مردم | سخنرانی عمومی</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>جامعه‌شناسان | مردم‌شناسان و باستان‌شناسان | جغرافی‌دانان | مورخان | دانشمندان علوم سیاسی | اقتصاددانان | اقتصاددانان محیط زیست | پژوهشگران نظرسنجی | برنامه‌ریزان شهری و منطقه‌ای | برنامه‌ریزان حمل‌ونقل | دستیاران پژوهشی علوم اجتماعی | تحلیلگران پژوهش بازار و متخصصان بازاریابی | روان‌شناسان بالینی و مشاوره | روان‌شناسان صنعتی-سازمانی | مدرسان جامعه‌شناسی، پس از متوسطه | مدرسان علوم سیاسی، پس از متوسطه | مدرسان مطالعات منطقه‌ای، قومی و فرهنگی، پس از متوسطه | آمارشناسان | تحلیلگران مدیریت | متخصصان آموزش بهداشت</t>
+          <t>جامعه‌شناسان | مردم‌شناسان و باستان‌شناسان | جغرافیدانان | مورخان | دانشمندان علوم سیاسی | اقتصاددانان | اقتصاددانان محیط‌زیست | پژوهشگران نظرسنجی | برنامه‌ریزان شهری و منطقه‌ای | برنامه‌ریزان حمل‌ونقل | دستیاران تحقیقات علوم اجتماعی | تحلیل‌گران تحقیقات بازار و متخصصان بازاریابی | روان‌شناسان بالینی و مشاوره | روان‌شناسان صنعتی-سازمانی | استادان جامعه‌شناسی، پس از متوسطه | استادان علوم سیاسی، پس از متوسطه | استادان مطالعات منطقه‌ای، قومی و فرهنگی، پس از متوسطه | آمارشناسان | تحلیل‌گران مدیریت | متخصصان آموزش بهداشت</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,27 +679,27 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | صحبت کردن | نوشتن | گوش دادن فعال | درک مطلب | یادگیری فعال | ریاضیات | نظارت | راهبردهای یادگیری</t>
+          <t>تفکر انتقادی | سخن گفتن | نگارش | گوش دادن فعال | درک مطلب | یادگیری فعال | ریاضیات | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>حمل‌ونقل | زبان انگلیسی | ریاضیات | جغرافیا | قانون و دولت | کامپیوتر و الکترونیک | مدیریت و اداره | مهندسی و فناوری | خدمات مشتری و شخصی | طراحی</t>
+          <t>حمل و نقل | زبان انگلیسی | ریاضیات | جغرافیا | قانون و دولت | رایانه و الکترونیک | مدیریت و اداره | مهندسی و فناوری | خدمات مشتری و شخصی | طراحی</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>بیان شفاهی | بیان نوشتاری | روانی ایده‌ها | استدلال قیاسی | استدلال استقرایی | درک شنیداری | درک نوشتاری | حساسیت به مسئله | تجسم | وضوح گفتار | دید نزدیک | اصالت | نظم‌دهی اطلاعات | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | دید دور | انعطاف‌پذیری بستار | استدلال ریاضی | توجه انتخابی | سرعت بستار | توانایی عددی</t>
+          <t>بیان شفاهی | بیان کتبی | روانی ایده‌ها | استدلال قیاسی | استدلال استقرایی | درک شفاهی | درک کتبی | حساسیت به مسئله | تجسم | وضوح گفتار | بینایی نزدیک | اصالت | ترتیب‌دهی اطلاعات | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | بینایی دور | انعطاف‌پذیری بستار | استدلال ریاضی | توجه انتخابی | سرعت بستار | توانایی عددی</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>ایمیل | بحث‌های رودررو با افراد و درون تیم‌ها | مکالمات تلفنی | صرف زمان برای نشستن | کار با یا مشارکت در یک گروه کاری یا تیم | محیط داخلی، دارای تهویه مطبوع | تماس با دیگران | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | تعامل با مشتریان خارجی یا عموم مردم | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | نامه‌ها و یادداشت‌های کتبی | تأثیر تصمیمات بر همکاران یا نتایج شرکت</t>
+          <t>ایمیل | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | صرف زمان برای نشستن | کار با یا مشارکت در یک گروه کاری یا تیم | محیط داخلی، دارای کنترل شرایط محیطی | ارتباط با دیگران | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | تعامل با مشتریان خارجی یا عموم مردم | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | نامه‌ها و یادداشت‌های کتبی | تأثیر تصمیمات بر همکاران یا نتایج شرکت</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>متخصصان بازسازی زمین‌های صنعتی و مدیران سایت | مدیران ارشد پایداری | تکنسین‌ها و کارشناسان مهندسی عمران | مهندسان عمران | تحلیلگران سیاست تغییرات اقلیمی | دانشمندان و متخصصان محیط زیست، شامل بهداشت | سرپرستان ردیف اول کارگران ماشین‌آلات و وسایل نقلیه حمل‌ونقل مواد | حمل‌ونقل‌کنندگان بار | تکنسین‌های هیدرولوژی | بوم‌شناسان صنعتی | متخصصان لجستیک | تحلیلگران لجستیک | مهندسان لجستیک | تحلیلگران مدیریت | متخصصان مدیریت پروژه | متخصصان پایداری | تکنسین‌های ترافیک | مهندسان حمل‌ونقل | مدیران حمل‌ونقل، ذخیره‌سازی و توزیع | برنامه‌ریزان شهری و منطقه‌ای</t>
+          <t>متخصصان بازآفرینی زمین‌های قهوه‌ای و مدیران سایت | مدیران ارشد پایداری | تکنسین‌ها و کارشناسان مهندسی عمران | مهندسان عمران | تحلیل‌گران سیاست تغییرات اقلیمی | دانشمندان و متخصصان محیط زیست، شامل بهداشت | سرپرستان خط اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابجایی مواد | متصدیان حمل و نقل | تکنسین‌های هیدرولوژی | بوم‌شناسان صنعتی | لجستیسین‌ها | تحلیلگران لجستیک | مهندسان لجستیک | تحلیل‌گران مدیریت | متخصصان مدیریت پروژه | متخصصان پایداری | تکنسین‌های ترافیک | مهندسان حمل و نقل | مدیران حمل‌ونقل، انبارداری و توزیع | برنامه‌ریزان شهری و منطقه‌ای</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | نوشتن | یادگیری فعال | نظارت | صحبت کردن</t>
+          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | نگارش | یادگیری فعال | نظارت | سخن گفتن</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -746,17 +746,17 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک شنیداری | بیان شفاهی | حساسیت به مسئله | دید نزدیک | درک نوشتاری | استدلال قیاسی | بیان نوشتاری | استدلال استقرایی | نظم‌دهی اطلاعات | ثبات بازو-دست | تشخیص رنگ بصری | انعطاف‌پذیری دسته‌بندی | توانایی عددی | استدلال ریاضی | اصالت | روانی ایده‌ها | وضوح گفتار | تشخیص گفتار | دید دور | دقت کنترل | توجه انتخابی | سرعت ادراکی | انعطاف‌پذیری بستار</t>
+          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | بینایی نزدیک | درک کتبی | استدلال قیاسی | بیان کتبی | استدلال استقرایی | ترتیب‌دهی اطلاعات | ثبات دست و بازو | تشخیص رنگ بصری | انعطاف‌پذیری دسته‌بندی | توانایی عددی | استدلال ریاضی | اصالت | روانی ایده‌ها | وضوح گفتار | تشخیص گفتار | بینایی دور | دقت کنترل | توجه انتخابی | سرعت ادراکی | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>بحث‌های رودررو با افراد و درون تیم‌ها | صرف زمان برای استفاده از دستان خود برای کار با، کنترل یا احساس اشیاء، ابزارها یا کنترل‌ها | فضای باز، در معرض تمام شرایط آب و هوایی | ایمیل | اهمیت دقیق یا صحیح بودن | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | پوشیدن تجهیزات حفاظتی یا ایمنی رایج مانند کفش ایمنی، عینک، دستکش، محافظ شنوایی، کلاه ایمنی یا جلیقه نجات | تماس با دیگران | در معرض آلاینده‌ها | آزادی در تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم | در معرض دماهای بسیار گرم یا سرد | محیط داخلی، دارای تهویه مطبوع نیست | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | سلامت و ایمنی سایر کارگران | در معرض صداها، سطوح نویز که حواس‌پرت‌کننده یا ناراحت‌کننده هستند | در یک وسیله نقلیه باز یا کار با تجهیزات | در معرض شرایط نوری بسیار روشن یا نامناسب | مکالمات تلفنی</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | فضای باز، در معرض تمام شرایط آب و هوایی | ایمیل | اهمیت دقیق یا درست بودن | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | ارتباط با دیگران | قرار گرفتن در معرض آلاینده‌ها | آزادی در تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | محیط داخلی، بدون کنترل شرایط محیطی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | سلامت و ایمنی سایر کارکنان | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | در یک وسیله نقلیه روباز یا کار با تجهیزات | قرار گرفتن در معرض شرایط نوری بسیار روشن یا ناکافی | مکالمات تلفنی</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>مهندسان کشاورزی | مدرسان علوم کشاورزی، پس از متوسطه | دانشمندان علوم دامی | تکنسین‌های فرآوری سوخت‌های زیستی | مدیران تولید سوخت‌های زیستی | تکنسین‌های زیستی | تکنسین‌های شیمی | شیمیدانان | تکنسین‌ها و کارشناسان مهندسی محیط زیست | تکنسین‌های علم و حفاظت محیط زیست، شامل بهداشت | کشاورزان، دامداران و سایر مدیران کشاورزی | کارگران مزرعه و کارگران، محصولات زراعی، نهالستان و گلخانه | سرپرستان ردیف اول کارگران کشاورزی، شیلات و جنگلداری | تکنسین‌های علوم غذایی | دانشمندان و فناوران علوم غذایی | تکنسین‌های جنگل و حفاظت | تکنسین‌های آزمایشگاه پزشکی و بالینی | میکروبیولوژیست‌ها | تکنسین‌های کشاورزی دقیق | دانشمندان خاک و گیاه</t>
+          <t>مهندسان کشاورزی | مدرسان علوم کشاورزی، پس از متوسطه | دانشمندان علوم دامی | تکنسین‌های فرآوری سوخت‌های زیستی | مدیران تولید سوخت‌های زیستی | تکنسین‌های زیستی | تکنسین‌های شیمی | شیمی‌دانان | تکنسین‌ها و کارشناسان مهندسی محیط زیست | تکنسین‌های علم و حفاظت محیط زیست، شامل بهداشت | کشاورزان، دامداران و سایر مدیران کشاورزی | کارگران کشاورزی و کارگران ساده، محصول، نهالستان و گلخانه | سرپرستان خط اول کارکنان کشاورزی، ماهیگیری و جنگل‌داری | تکنسین‌های علوم غذایی | دانشمندان و تکنولوژیست‌های علوم غذایی | تکنسین‌های جنگل و حفاظت | تکنیسین‌های آزمایشگاه پزشکی و بالینی | میکروبیولوژیست‌ها | تکنسین‌های کشاورزی دقیق | دانشمندان خاک و گیاه</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,27 +793,27 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>درک مطلب | گوش دادن فعال | صحبت کردن | تفکر انتقادی | نوشتن | یادگیری فعال | ریاضیات | نظارت | راهبردهای یادگیری</t>
+          <t>درک مطلب | گوش دادن فعال | سخن گفتن | تفکر انتقادی | نگارش | یادگیری فعال | ریاضیات | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>خدمات مشتری و شخصی | کامپیوتر و الکترونیک | فروش و بازاریابی | زبان انگلیسی | ریاضیات | مهندسی و فناوری | زیست‌شناسی | تولید مواد غذایی | مکانیک | جغرافیا | آموزش و پرورش | شیمی | تولید و فرآوری</t>
+          <t>خدمات مشتری و شخصی | رایانه و الکترونیک | فروش و بازاریابی | زبان انگلیسی | ریاضیات | مهندسی و فناوری | زیست‌شناسی | تولید مواد غذایی | مکانیک | جغرافیا | آموزش و پرورش | شیمی | تولید و فرآوری</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>استدلال قیاسی | استدلال استقرایی | درک شنیداری | درک نوشتاری | بیان شفاهی | بیان نوشتاری | دید نزدیک | نظم‌دهی اطلاعات | حساسیت به مسئله | وضوح گفتار | سرعت ادراکی | انعطاف‌پذیری بستار | استدلال ریاضی | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | مهارت دستی | ثبات بازو-دست | دقت کنترل | توجه انتخابی | تجسم | سرعت بستار | توانایی عددی | دید دور | تشخیص گفتار</t>
+          <t>استدلال قیاسی | استدلال استقرایی | درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | بینایی نزدیک | ترتیب‌دهی اطلاعات | حساسیت به مسئله | وضوح گفتار | سرعت ادراکی | انعطاف‌پذیری بستار | استدلال ریاضی | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | مهارت دستی | ثبات دست و بازو | دقت کنترل | توجه انتخابی | تجسم | سرعت بستار | توانایی عددی | بینایی دور | تشخیص گفتار</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>مکالمات تلفنی | ایمیل | بحث‌های رودررو با افراد و درون تیم‌ها | تماس با دیگران | آزادی در تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم | تعامل با مشتریان خارجی یا عموم مردم | تعیین وظایف، اولویت‌ها و اهداف | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | اهمیت دقیق یا صحیح بودن | تناوب تصمیم‌گیری | فضای باز، در معرض تمام شرایط آب و هوایی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فضای باز، زیر پوشش</t>
+          <t>مکالمات تلفنی | ایمیل | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | آزادی در تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم | تعامل با مشتریان خارجی یا عموم مردم | تعیین وظایف، اولویت‌ها و اهداف | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | اهمیت دقیق یا درست بودن | فراوانی تصمیم‌گیری | فضای باز، در معرض تمام شرایط آب و هوایی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فضای باز، زیر سقف</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>مهندسان کشاورزی | تکنسین‌های کشاورزی | دانشمندان حفاظت | دانشمندان داده | تکنسین‌ها و کارشناسان مهندسی محیط زیست | تکنسین‌های علم و حفاظت محیط زیست، شامل بهداشت | دانشمندان و متخصصان محیط زیست، شامل بهداشت | کشاورزان، دامداران و سایر مدیران کشاورزی | کارگران مزرعه و کارگران، محصولات زراعی، نهالستان و گلخانه | دانشمندان و فناوران علوم غذایی | تکنسین‌های جنگل و حفاظت | تکنسین‌های زمین‌شناسی، به جز تکنسین‌های هیدرولوژی | تکنسین‌های هیدرولوژی | بوم‌شناسان صنعتی | تکنسین‌ها و کارشناسان مهندسی صنعتی | مهندسان صنعتی | مدیران مراتع | دانشمندان و فناوران سنجش از دور | تکنسین‌های سنجش از دور | دانشمندان خاک و گیاه</t>
+          <t>مهندسان کشاورزی | تکنسین‌های کشاورزی | دانشمندان حفاظت | دانشمندان داده | تکنسین‌ها و کارشناسان مهندسی محیط زیست | تکنسین‌های علم و حفاظت محیط زیست، شامل بهداشت | دانشمندان و متخصصان محیط زیست، شامل بهداشت | کشاورزان، دامداران و سایر مدیران کشاورزی | کارگران کشاورزی و کارگران ساده، محصول، نهالستان و گلخانه | دانشمندان و تکنولوژیست‌های علوم غذایی | تکنسین‌های جنگل و حفاظت | تکنسین‌های زمین‌شناسی، به استثنای تکنسین‌های هیدرولوژی | تکنسین‌های هیدرولوژی | بوم‌شناسان صنعتی | تکنسین‌ها و کارشناسان مهندسی صنایع | مهندسان صنایع | مدیران مراتع | دانشمندان و فناوران سنجش از دور | تکنسین‌های سنجش از دور | دانشمندان خاک و گیاه</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,27 +850,27 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>درک مطلب | گوش دادن فعال | نوشتن | صحبت کردن | تفکر انتقادی | علم | نظارت | یادگیری فعال</t>
+          <t>درک مطلب | گوش دادن فعال | نگارش | سخن گفتن | تفکر انتقادی | علوم | نظارت | یادگیری فعال</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>تولید مواد غذایی | تولید و فرآوری | شیمی | زبان انگلیسی | کامپیوتر و الکترونیک | زیست‌شناسی | ریاضیات</t>
+          <t>تولید مواد غذایی | تولید و فرآوری | شیمی | زبان انگلیسی | رایانه و الکترونیک | زیست‌شناسی | ریاضیات</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>دید نزدیک | درک شنیداری | درک نوشتاری | بیان شفاهی | بیان نوشتاری | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | تشخیص رنگ بصری | تشخیص گفتار | وضوح گفتار | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | نظم‌دهی اطلاعات | سرعت ادراکی | انعطاف‌پذیری بستار | توانایی عددی | استدلال ریاضی</t>
+          <t>بینایی نزدیک | درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | تشخیص رنگ بصری | تشخیص گفتار | وضوح گفتار | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | سرعت ادراکی | انعطاف‌پذیری بستار | توانایی عددی | استدلال ریاضی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>بحث‌های رودررو با افراد و درون تیم‌ها | محیط داخلی، دارای تهویه مطبوع | پوشیدن تجهیزات حفاظتی یا ایمنی رایج مانند کفش ایمنی، عینک، دستکش، محافظ شنوایی، کلاه ایمنی یا جلیقه نجات | ایمیل | کار با یا مشارکت در یک گروه کاری یا تیم | تماس با دیگران | اهمیت دقیق یا صحیح بودن | اهمیت تکرار کارهای مشابه | فشار زمانی | تناوب تصمیم‌گیری | آزادی در تصمیم‌گیری | نتایج کاری و خروجی‌های سایر کارگران | مکالمات تلفنی | سلامت و ایمنی سایر کارگران | صرف زمان برای استفاده از دستان خود برای کار با، کنترل یا احساس اشیاء، ابزارها یا کنترل‌ها | تأثیر تصمیمات بر همکاران یا نتایج شرکت | صرف زمان برای راه رفتن یا دویدن | صرف زمان برای ایستادن | در معرض صداها، سطوح نویز که حواس‌پرت‌کننده یا ناراحت‌کننده هستند | تعیین وظایف، اولویت‌ها و اهداف | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | در معرض آلاینده‌ها | سرعت تعیین‌شده توسط سرعت تجهیزات</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | ایمیل | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | اهمیت دقیق یا درست بودن | اهمیت تکرار وظایف یکسان | فشار زمانی | فراوانی تصمیم‌گیری | آزادی در تصمیم‌گیری | پیامدهای کاری و نتایج سایر کارکنان | مکالمات تلفنی | سلامت و ایمنی سایر کارکنان | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | تأثیر تصمیمات بر همکاران یا نتایج شرکت | صرف زمان برای راه رفتن یا دویدن | صرف زمان برای ایستادن | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | تعیین وظایف، اولویت‌ها و اهداف | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | قرار گرفتن در معرض آلاینده‌ها | سرعت تعیین‌شده توسط سرعت تجهیزات</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>بازرسان کشاورزی | تکنسین‌های کشاورزی | دانشمندان علوم دامی | تکنسین‌های فرآوری سوخت‌های زیستی | تکنسین‌های زیستی | تکنسین‌ها و کارشناسان کالیبراسیون | تکنسین‌های شیمی | شیمیدانان | دست‌اندرکاران دسته‌ای مواد غذایی | دانشمندان و فناوران علوم غذایی | اپراتورها و متصدیان ماشین‌آلات برشته‌کاری، پخت و خشک‌کردن مواد غذایی و تنباکو | درجه‌بندی‌کنندگان و مرتب‌کنندگان محصولات کشاورزی | تکنسین‌ها و کارشناسان مهندسی صنعتی | بازرسان، آزمایش‌کنندگان، مرتب‌کنندگان، نمونه‌گیران و وزن‌کنندگان | تکنسین‌های آزمایشگاه پزشکی و بالینی | کارشناسان آزمایشگاه پزشکی و بالینی | میکروبیولوژیست‌ها | تحلیلگران کنترل کیفیت | مدیران سیستم‌های کنترل کیفیت | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات جداسازی، فیلتر کردن، شفاف‌سازی، رسوب‌دهی و تقطیر</t>
+          <t>بازرسان کشاورزی | تکنسین‌های کشاورزی | دانشمندان علوم دامی | تکنسین‌های فرآوری سوخت‌های زیستی | تکنسین‌های زیستی | تکنولوژیست‌ها و تکنسین‌های کالیبراسیون | تکنسین‌های شیمی | شیمی‌دانان | بچ‌سازان مواد غذایی | دانشمندان و تکنولوژیست‌های علوم غذایی | اپراتورها و متصدیان ماشین‌های برشته‌کاری، پخت و خشک‌کردن مواد غذایی و تنباکو | درجه‌بندها و مرتب‌کنندگان محصولات کشاورزی | تکنسین‌ها و کارشناسان مهندسی صنایع | بازرسان، آزمایش‌کنندگان، سورترها، نمونه‌برداران و توزین‌کنندگان | تکنیسین‌های آزمایشگاه پزشکی و بالینی | تکنولوژیست‌های آزمایشگاه پزشکی و بالینی | میکروبیولوژیست‌ها | تحلیل‌گران کنترل کیفیت | مدیران سیستم‌های کنترل کیفیت | تنظیم‌کاران، اپراتورها و متصدیان ماشین‌آلات جداسازی، فیلتراسیون، زلال‌سازی، ته‌نشینی و تقطیر</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,27 +907,27 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | علم | گوش دادن فعال | یادگیری فعال | نوشتن | صحبت کردن | نظارت | ریاضیات</t>
+          <t>درک مطلب | تفکر انتقادی | علوم | گوش دادن فعال | یادگیری فعال | نگارش | سخن گفتن | نظارت | ریاضیات</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>زیست‌شناسی | زبان انگلیسی | ریاضیات | کامپیوتر و الکترونیک | شیمی</t>
+          <t>زیست‌شناسی | زبان انگلیسی | ریاضیات | رایانه و الکترونیک | شیمی</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>دید نزدیک | درک شنیداری | استدلال استقرایی | بیان شفاهی | نظم‌دهی اطلاعات | بیان نوشتاری | استدلال قیاسی | درک نوشتاری | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | حساسیت به مسئله | توجه انتخابی | انعطاف‌پذیری بستار | استدلال ریاضی | روانی ایده‌ها | تشخیص رنگ بصری | مهارت انگشت | ثبات بازو-دست | سرعت ادراکی | توانایی عددی | تجسم</t>
+          <t>بینایی نزدیک | درک شفاهی | استدلال استقرایی | بیان شفاهی | ترتیب‌دهی اطلاعات | بیان کتبی | استدلال قیاسی | درک کتبی | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | حساسیت به مسئله | توجه انتخابی | انعطاف‌پذیری بستار | استدلال ریاضی | روانی ایده‌ها | تشخیص رنگ بصری | مهارت انگشتان | ثبات دست و بازو | سرعت ادراکی | توانایی عددی | تجسم</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>ایمیل | بحث‌های رودررو با افراد و درون تیم‌ها | اهمیت دقیق یا صحیح بودن | محیط داخلی، دارای تهویه مطبوع | پوشیدن تجهیزات حفاظتی یا ایمنی رایج مانند کفش ایمنی، عینک، دستکش، محافظ شنوایی، کلاه ایمنی یا جلیقه نجات | تماس با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف</t>
+          <t>ایمیل | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن | محیط داخلی، دارای کنترل شرایط محیطی | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>تکنسین‌های کشاورزی | بیوشیمی‌دانان و بیوفیزیک‌دانان | مهندسان زیستی و مهندسان پزشکی | دانشمندان بیوانفورماتیک | تکنسین‌های بیوانفورماتیک | مدرسان علوم زیستی، پس از متوسطه | زیست‌شناسان | تکنسین‌ها و کارشناسان کالیبراسیون | تکنسین‌های شیمی | شیمیدانان | کارشناسان سیتوژنتیک | ژنتیک‌دانان | تکنسین‌های بافت‌شناسی | کارشناسان بافت‌شناسی | تکنسین‌های آزمایشگاه پزشکی و بالینی | کارشناسان آزمایشگاه پزشکی و بالینی | میکروبیولوژیست‌ها | زیست‌شناسان مولکولی و سلولی | تکنسین‌ها و کارشناسان مهندسی نانوتکنولوژی | مدیران علوم طبیعی</t>
+          <t>تکنسین‌های کشاورزی | بیوشیمی‌دانان و بیوفیزیک‌دانان | مهندسان زیستی و مهندسان زیست‌پزشکی | دانشمندان بیوانفورماتیک | تکنسین‌های بیوانفورماتیک | مدرسان علوم زیستی، پس از متوسطه | زیست‌شناسان | تکنولوژیست‌ها و تکنسین‌های کالیبراسیون | تکنسین‌های شیمی | شیمی‌دانان | تکنولوژیست‌های سیتوژنتیک | ژنتیک‌دان‌ها | تکنیسین‌های هیستولوژی | هیستوتکنولوژیست‌ها | تکنیسین‌های آزمایشگاه پزشکی و بالینی | تکنولوژیست‌های آزمایشگاه پزشکی و بالینی | میکروبیولوژیست‌ها | زیست‌شناسان مولکولی و سلولی | تکنسین‌ها و کارشناسان مهندسی نانوتکنولوژی | مدیران علوم طبیعی</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,27 +964,27 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>علم | تفکر انتقادی | درک مطلب | گوش دادن فعال | نوشتن | نظارت | صحبت کردن | یادگیری فعال | راهبردهای یادگیری | ریاضیات</t>
+          <t>علوم | تفکر انتقادی | درک مطلب | گوش دادن فعال | نگارش | نظارت | سخن گفتن | یادگیری فعال | راهبردهای یادگیری | ریاضیات</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>شیمی | زبان انگلیسی | ریاضیات | کامپیوتر و الکترونیک</t>
+          <t>شیمی | زبان انگلیسی | ریاضیات | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>دید نزدیک | درک نوشتاری | بیان نوشتاری | درک شنیداری | حساسیت به مسئله | استدلال استقرایی | نظم‌دهی اطلاعات | بیان شفاهی | استدلال قیاسی | انعطاف‌پذیری دسته‌بندی | وضوح گفتار | تشخیص گفتار | دقت کنترل | تجسم | انعطاف‌پذیری بستار | استدلال ریاضی | مهارت انگشت | مهارت دستی | ثبات بازو-دست | توجه انتخابی | روانی ایده‌ها | سرعت ادراکی | سرعت بستار | توانایی عددی | اصالت | تشخیص رنگ بصری</t>
+          <t>بینایی نزدیک | درک کتبی | بیان کتبی | درک شفاهی | حساسیت به مسئله | استدلال استقرایی | ترتیب‌دهی اطلاعات | بیان شفاهی | استدلال قیاسی | انعطاف‌پذیری دسته‌بندی | وضوح گفتار | تشخیص گفتار | دقت کنترل | تجسم | انعطاف‌پذیری بستار | استدلال ریاضی | مهارت انگشتان | مهارت دستی | ثبات دست و بازو | توجه انتخابی | روانی ایده‌ها | سرعت ادراکی | سرعت بستار | توانایی عددی | اصالت | تشخیص رنگ بصری</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>پوشیدن تجهیزات حفاظتی یا ایمنی رایج مانند کفش ایمنی، عینک، دستکش، محافظ شنوایی، کلاه ایمنی یا جلیقه نجات | ایمیل | بحث‌های رودررو با افراد و درون تیم‌ها | محیط داخلی، دارای تهویه مطبوع | در معرض آلاینده‌ها | اهمیت دقیق یا صحیح بودن | کار با یا مشارکت در یک گروه کاری یا تیم | در معرض شرایط خطرناک | فشار زمانی | سلامت و ایمنی سایر کارگران | صرف زمان برای استفاده از دستان خود برای کار با، کنترل یا احساس اشیاء، ابزارها یا کنترل‌ها | تماس با دیگران | آزادی در تصمیم‌گیری | پیامد خطا | تأثیر تصمیمات بر همکاران یا نتایج شرکت | صرف زمان برای ایستادن | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | اهمیت تکرار کارهای مشابه | در معرض صداها، سطوح نویز که حواس‌پرت‌کننده یا ناراحت‌کننده هستند</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | ایمیل | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | قرار گرفتن در معرض آلاینده‌ها | اهمیت دقیق یا درست بودن | کار با یا مشارکت در یک گروه کاری یا تیم | قرار گرفتن در معرض شرایط خطرناک | فشار زمانی | سلامت و ایمنی سایر کارکنان | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | ارتباط با دیگران | آزادی در تصمیم‌گیری | پیامد خطا | تأثیر تصمیمات بر همکاران یا نتایج شرکت | صرف زمان برای ایستادن | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | اهمیت تکرار وظایف یکسان | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>تکنسین‌ها و کارشناسان مهندسی هوافضا و عملیات | تکنسین‌های کشاورزی | تکنسین‌های زیستی | تکنسین‌ها و کارشناسان کالیبراسیون | مهندسان شیمی | اپراتورها و متصدیان تجهیزات شیمیایی | اپراتورهای کارخانه و سیستم‌های شیمیایی | شیمیدانان | تکنسین‌های علم و حفاظت محیط زیست، شامل بهداشت | تکنسین‌های علوم غذایی | تکنسین‌ها و کارشناسان مهندسی صنعتی | مهندسان صنعتی | بازرسان، آزمایش‌کنندگان، مرتب‌کنندگان، نمونه‌گیران و وزن‌کنندگان | مهندسان مواد | دانشمندان مواد | تکنسین‌ها و کارشناسان مهندسی مکانیک | تکنسین‌های آزمایشگاه پزشکی و بالینی | کارشناسان آزمایشگاه پزشکی و بالینی | تکنسین‌ها و کارشناسان مهندسی نانوتکنولوژی | تحلیلگران کنترل کیفیت</t>
+          <t>تکنسین‌ها و کارشناسان مهندسی و عملیات هوافضا | تکنسین‌های کشاورزی | تکنسین‌های زیستی | تکنولوژیست‌ها و تکنسین‌های کالیبراسیون | مهندسان شیمی | متصدیان و اپراتورهای تجهیزات شیمیایی | اپراتورهای کارخانه و سامانه‌های شیمیایی | شیمی‌دانان | تکنسین‌های علم و حفاظت محیط زیست، شامل بهداشت | تکنسین‌های علوم غذایی | تکنسین‌ها و کارشناسان مهندسی صنایع | مهندسان صنایع | بازرسان، آزمایش‌کنندگان، سورترها، نمونه‌برداران و توزین‌کنندگان | مهندسان مواد | دانشمندان مواد | تکنسین‌ها و کارشناسان مهندسی مکانیک | تکنیسین‌های آزمایشگاه پزشکی و بالینی | تکنولوژیست‌های آزمایشگاه پزشکی و بالینی | تکنسین‌ها و کارشناسان مهندسی نانوتکنولوژی | تحلیل‌گران کنترل کیفیت</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,27 +1021,27 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>درک مطلب | گوش دادن فعال | نوشتن | صحبت کردن | تفکر انتقادی | نظارت | علم | ریاضیات | یادگیری فعال | راهبردهای یادگیری</t>
+          <t>درک مطلب | گوش دادن فعال | نگارش | سخن گفتن | تفکر انتقادی | نظارت | علوم | ریاضیات | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>خدمات مشتری و شخصی | زبان انگلیسی | شیمی | زیست‌شناسی | قانون و دولت | کامپیوتر و الکترونیک | ریاضیات | ایمنی و امنیت عمومی | مهندسی و فناوری</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | شیمی | زیست‌شناسی | قانون و دولت | رایانه و الکترونیک | ریاضیات | ایمنی و امنیت عمومی | مهندسی و فناوری</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>درک شنیداری | درک نوشتاری | بیان شفاهی | دید نزدیک | بیان نوشتاری | استدلال قیاسی | استدلال استقرایی | وضوح گفتار | حساسیت به مسئله | تشخیص گفتار | نظم‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار | توانایی عددی | استدلال ریاضی | روانی ایده‌ها | دید دور | ثبات بازو-دست | توجه انتخابی | تجسم | سرعت ادراکی</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بینایی نزدیک | بیان کتبی | استدلال قیاسی | استدلال استقرایی | وضوح گفتار | حساسیت به مسئله | تشخیص گفتار | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار | توانایی عددی | استدلال ریاضی | روانی ایده‌ها | بینایی دور | ثبات دست و بازو | توجه انتخابی | تجسم | سرعت ادراکی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | بحث‌های رودررو با افراد و درون تیم‌ها | فشار زمانی | محیط داخلی، دارای تهویه مطبوع | اهمیت دقیق یا صحیح بودن | نامه‌ها و یادداشت‌های کتبی | تماس با دیگران | تعامل با مشتریان خارجی یا عموم مردم | کار با یا مشارکت در یک گروه کاری یا تیم | سلامت و ایمنی سایر کارگران | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | پوشیدن تجهیزات حفاظتی یا ایمنی رایج مانند کفش ایمنی، عینک، دستکش، محافظ شنوایی، کلاه ایمنی یا جلیقه نجات | فضای باز، در معرض تمام شرایط آب و هوایی | محیط داخلی، دارای تهویه مطبوع نیست | تأثیر تصمیمات بر همکاران یا نتایج شرکت | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور</t>
+          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | فشار زمانی | محیط داخلی، دارای کنترل شرایط محیطی | اهمیت دقیق یا درست بودن | نامه‌ها و یادداشت‌های کتبی | ارتباط با دیگران | تعامل با مشتریان خارجی یا عموم مردم | کار با یا مشارکت در یک گروه کاری یا تیم | سلامت و ایمنی سایر کارکنان | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | فضای باز، در معرض تمام شرایط آب و هوایی | محیط داخلی، بدون کنترل شرایط محیطی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>تکنسین‌های زیستی | متخصصان بازسازی زمین‌های صنعتی و مدیران سایت | تکنسین‌های شیمی | دانشمندان حفاظت | بازرسان انطباق زیست‌محیطی | تکنسین‌ها و کارشناسان مهندسی محیط زیست | مهندسان محیط زیست | دانشمندان و متخصصان محیط زیست، شامل بهداشت | تکنسین‌های زمین‌شناسی، به جز تکنسین‌های هیدرولوژی | کارگران حذف مواد خطرناک | مهندسان بهداشت و ایمنی، به جز مهندسان و بازرسان ایمنی معدن | تکنسین‌های هیدرولوژی | هیدرولوژیست‌ها | بوم‌شناسان صنعتی | مهندسان هسته‌ای | تکنسین‌های نظارت هسته‌ای | متخصصان بهداشت و ایمنی شغلی | متخصصان منابع آب | اپراتورهای کارخانه و سیستم‌های تصفیه آب و فاضلاب | مهندسان آب/فاضلاب</t>
+          <t>تکنسین‌های زیستی | متخصصان بازآفرینی زمین‌های قهوه‌ای و مدیران سایت | تکنسین‌های شیمی | دانشمندان حفاظت | بازرسان انطباق زیست‌محیطی | تکنسین‌ها و کارشناسان مهندسی محیط زیست | مهندسان محیط زیست | دانشمندان و متخصصان محیط زیست، شامل بهداشت | تکنسین‌های زمین‌شناسی، به استثنای تکنسین‌های هیدرولوژی | کارگران حذف مواد خطرناک | مهندسان بهداشت و ایمنی، به جز مهندسان و بازرسان ایمنی معدن | تکنسین‌های هیدرولوژی | آب‌شناسان | بوم‌شناسان صنعتی | مهندسان هسته‌ای | تکنسین‌های نظارت هسته‌ای | متخصصان بهداشت و ایمنی شغلی | متخصصان منابع آب | اپراتورهای سیستم و تصفیه‌خانه آب و فاضلاب | مهندسان آب و فاضلاب</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">

--- a/data_extactor/batch_10_fa/batch_0026_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0026_fa.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>درک مطلب | نگارش | تفکر انتقادی | شنیدن فعال | یادگیری فعال | سخن گفتن | راهبردهای یادگیری | نظارت</t>
+          <t>درک مطلب | نگارش | تفکر انتقادی | گوش دادن فعال | یادگیری فعال | سخن گفتن | راهبردهای یادگیری | نظارت</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>تاریخ و باستان‌شناسی | زبان انگلیسی | جامعه‌شناسی و مردم‌شناسی | جغرافیا | مدیریت و امور اداری | آموزش و تدریس | ارتباطات و رسانه</t>
+          <t>تاریخ و باستان‌شناسی | زبان انگلیسی | جامعه‌شناسی و انسان‌شناسی | جغرافیا | اداری | آموزش و پرورش | ارتباطات و رسانه</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک کتبی | بیان کتبی | درک شفاهی | بیان شفاهی | دید نزدیک | استدلال استقرایی | وضوح گفتار | استدلال قیاسی | تشخیص گفتار | مرتب‌سازی اطلاعات | روانی و سیالی ایده‌ها | انعطاف‌پذیری در دسته‌بندی | حساسیت به مسئله | توجه انتخابی</t>
+          <t>درک کتبی | بیان کتبی | درک شفاهی | بیان شفاهی | بینایی نزدیک | استدلال استقرایی | وضوح گفتار | استدلال قیاسی | تشخیص گفتار | ترتیب‌دهی اطلاعات | روانی ایده‌ها | انعطاف‌پذیری دسته‌بندی | حساسیت به مسئله | توجه انتخابی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>مردم‌شناسان و باستان‌شناسان | استادان مردم‌شناسی و باستان‌شناسی دانشگاه | استادان معماری دانشگاه | آرشیوداران و بایگان‌های اسناد | استادان مطالعات منطقه‌ای، قومی و فرهنگی دانشگاه | موزه‌داران | ویراستاران | استادان زبان و ادبیات انگلیسی دانشگاه | جغرافیدانان | استادان جغرافیای دانشگاه | استادان تاریخ دانشگاه | کتابداران و کارشناسان مجموعه‌های رسانه‌ای | استادان علوم کتابداری دانشگاه | تکنسین‌ها و مرمت‌کاران موزه | تحلیل‌گران خبر، گزارشگران و روزنامه‌نگاران | شاعران، ترانه‌سرایان و نویسندگان خلاق | دستیاران پژوهشی علوم اجتماعی | جامعه‌شناسان | استادان جامعه‌شناسی دانشگاه | راهنمایان تور و گردشگری</t>
+          <t>انسان‌شناسان و باستان‌شناسان | استادان انسان‌شناسی و باستان‌شناسی دانشگاه | استادان و مدرسان معماری در دانشگاه‌ها و مراکز آموزش عالی | کارشناسان اسناد و آرشیو | استادان مطالعات منطقه‌ای، قومی و فرهنگی دانشگاه | موزه‌داران | ویراستاران | مدرسان زبان و ادبیات انگلیسی در دانشگاه‌ها و مراکز آموزش عالی | جغرافیدانان | استادان جغرافیای دانشگاه | مدرسان تاریخ در دانشگاه‌ها و مراکز آموزش عالی | کتابداران و کارشناسان مجموعه‌های رسانه‌ای | مدرسان علم اطلاعات و دانش‌شناسی در دانشگاه‌ها و مراکز آموزش عالی | تکنسین‌ها و مرمت‌گران موزه | تحلیل‌گران خبر، خبرنگاران و روزنامه‌نگاران | شاعران، ترانه‌سرایان و نویسندگان خلاق | کمک‌کارشناسان و دستیاران پژوهشی علوم اجتماعی | جامعه‌شناسان | استادان جامعه‌شناسی دانشگاه | راهنمایان تور و گردشگری</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | سخن گفتن | یادگیری فعال | تفکر انتقادی | نگارش | راهبردهای یادگیری | ریاضیات</t>
+          <t>درک مطلب | گوش دادن فعال | سخن گفتن | یادگیری فعال | تفکر انتقادی | نگارش | راهبردهای یادگیری | ریاضیات</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>حقوق و امور دولتی | زبان انگلیسی | آموزش و تدریس | تاریخ و باستان‌شناسی | ریاضیات | ارتباطات و رسانه | جامعه‌شناسی و مردم‌شناسی | جغرافیا | فلسفه و الهیات | رایانه و الکترونیک</t>
+          <t>قانون و دولت | زبان انگلیسی | آموزش و پرورش | تاریخ و باستان‌شناسی | ریاضیات | ارتباطات و رسانه | جامعه‌شناسی و انسان‌شناسی | جغرافیا | فلسفه و الهیات | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک کتبی | درک شفاهی | بیان شفاهی | بیان کتبی | استدلال استقرایی | وضوح گفتار | تشخیص گفتار | استدلال قیاسی | دید نزدیک | حساسیت به مسئله | مرتب‌سازی اطلاعات | ابتکار و اصالت | روانی و سیالی ایده‌ها | انعطاف‌پذیری در دسته‌بندی | استدلال ریاضی</t>
+          <t>درک کتبی | درک شفاهی | بیان شفاهی | بیان کتبی | استدلال استقرایی | وضوح گفتار | تشخیص گفتار | استدلال قیاسی | بینایی نزدیک | حساسیت به مسئله | ترتیب‌دهی اطلاعات | اصالت | روانی ایده‌ها | انعطاف‌پذیری دسته‌بندی | استدلال ریاضی</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>استادان مدیریت و بازرگانی دانشگاه | مدیران ارشد اجرایی | تحلیل‌گران سیاست‌گذاری تغییرات اقلیمی | استادان علوم قضایی و انتظامی دانشگاه | استادان اقتصاد دانشگاه | اقتصاددانان | اقتصاددانان محیط زیست | کارشناسان امور اداری و فرصت‌های برابر | استادان تاریخ دانشگاه | تحلیل‌گران داده‌های اطلاعاتی و امنیتی | کارشناسان روابط کار | استادان حقوق دانشگاه | قانون‌گذاران و نمایندگان مجلس | تحلیل‌گران مدیریت و فرایندها | استادان علوم سیاسی دانشگاه | مدیران روابط عمومی | جامعه‌شناسان | استادان جامعه‌شناسی دانشگاه | پژوهشگران نظرسنجی و افکارسنجی | برنامه‌ریزان شهری و منطقه‌ای</t>
+          <t>استادان علوم اداری و مدیریت، آموزش عالی | مدیران عامل و مدیران ارشد اجرایی | تحلیل‌گران خط‌مشی تغییر اقلیم | مدرسان حقوق جزا، جرم‌شناسی و علوم انتظامی در دانشگاه‌ها و مراکز آموزش عالی | استادان اقتصاد دانشگاه | اقتصاددانان | اقتصاددانان محیط زیست | کارشناسان امور انطباق و صیانت از فرصت‌های برابر استخدامی | مدرسان تاریخ در دانشگاه‌ها و مراکز آموزش عالی | تحلیل‌گران داده‌ها و اطلاعات امنیتی | کارشناسان روابط کار و امور تشکل‌های کارگری | مدرسان حقوق در دانشگاه‌ها و مراکز آموزش عالی | نمایندگان مجالس و شوراهای قانون‌گذاری | کارشناسان تحلیل مدیریت و روش‌ها | استادان علوم سیاسی دانشگاه | مدیران روابط عمومی | جامعه‌شناسان | استادان جامعه‌شناسی دانشگاه | پژوهشگران پیمایشی و افکارسنجی | برنامه‌ریزان شهری و منطقه‌ای</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | شنیدن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
+          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>جامعه‌شناسی و مردم‌شناسی | زبان انگلیسی | ریاضیات | روان‌شناسی | تاریخ و باستان‌شناسی | جغرافیا | حقوق و امور دولتی | آموزش و تدریس | رایانه و الکترونیک</t>
+          <t>جامعه‌شناسی و انسان‌شناسی | زبان انگلیسی | ریاضیات | روان‌شناسی | تاریخ و باستان‌شناسی | جغرافیا | قانون و دولت | آموزش و پرورش | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات | حساسیت به مسئله | دید نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری در دسته‌بندی | روانی و سیالی ایده‌ها | ابتکار و اصالت | توجه انتخابی | تسهیم توجه | تجسم و تصویرسازی ذهنی | حافظه و به‌خاطرسپاری | استدلال ریاضی | سرعت کار با اعداد | سرعت ادراک | انعطاف‌پذیری در تحلیل الگوها</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | توجه انتخابی | تقسیم توجه | تجسم | حفظ کردن | استدلال ریاضی | توانایی عددی | سرعت ادراکی | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>جامعه‌شناسان | مردم‌شناسان و باستان‌شناسان | جغرافیدانان | مورخان | دانشمندان و پژوهشگران علوم سیاسی | اقتصاددانان | اقتصاددانان محیط زیست | پژوهشگران نظرسنجی و افکارسنجی | برنامه‌ریزان شهری و منطقه‌ای | برنامه‌ریزان حمل و نقل | دستیاران پژوهشی علوم اجتماعی | تحلیل‌گران پژوهش بازار و متخصصان بازاریابی | روان‌شناسان بالینی و مشاور | روان‌شناسان صنعتی و سازمانی | استادان جامعه‌شناسی دانشگاه | استادان علوم سیاسی دانشگاه | استادان مطالعات منطقه‌ای، قومی و فرهنگی دانشگاه | آمارشناسان | تحلیل‌گران مدیریت و فرایندها | کارشناسان آموزش سلامت و بهداشت</t>
+          <t>جامعه‌شناسان | انسان‌شناسان و باستان‌شناسان | جغرافیدانان | مورخان | دانشمندان و پژوهشگران علوم سیاسی | اقتصاددانان | اقتصاددانان محیط زیست | پژوهشگران پیمایشی و افکارسنجی | برنامه‌ریزان شهری و منطقه‌ای | برنامه‌ریزان سیستم‌های حمل‌ونقل | کمک‌کارشناسان و دستیاران پژوهشی علوم اجتماعی | کارشناسان تحلیل تحقیقات بازار و بازاریابی | روان‌شناسان بالینی و مشاوران سلامت روان | روان‌شناسان صنعتی و سازمانی | استادان جامعه‌شناسی دانشگاه | استادان علوم سیاسی دانشگاه | استادان مطالعات منطقه‌ای، قومی و فرهنگی دانشگاه | کارشناسان آمار | کارشناسان تحلیل مدیریت و روش‌ها | کارشناسان آموزش بهداشت و ارتقای سلامت</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن گفتن | نگارش | شنیدن فعال | درک مطلب | یادگیری فعال | ریاضیات | نظارت | راهبردهای یادگیری</t>
+          <t>تفکر انتقادی | سخن گفتن | نگارش | گوش دادن فعال | درک مطلب | یادگیری فعال | ریاضیات | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>حمل و نقل | زبان انگلیسی | ریاضیات | جغرافیا | حقوق و امور دولتی | رایانه و الکترونیک | مدیریت و امور اداری | مهندسی و فناوری | خدمات مشتریان و خدمات فردی | طراحی</t>
+          <t>حمل و نقل | زبان انگلیسی | ریاضیات | جغرافیا | قانون و دولت | رایانه و الکترونیک | مدیریت و اداره | مهندسی و فناوری | خدمات مشتری و شخصی | طراحی</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>بیان شفاهی | بیان کتبی | روانی و سیالی ایده‌ها | استدلال قیاسی | استدلال استقرایی | درک شفاهی | درک کتبی | حساسیت به مسئله | تجسم و تصویرسازی ذهنی | وضوح گفتار | دید نزدیک | ابتکار و اصالت | مرتب‌سازی اطلاعات | تشخیص گفتار | انعطاف‌پذیری در دسته‌بندی | دید دور | انعطاف‌پذیری در تحلیل الگوها | استدلال ریاضی | توجه انتخابی | سرعت درک الگوها | سرعت کار با اعداد</t>
+          <t>بیان شفاهی | بیان کتبی | روانی ایده‌ها | استدلال قیاسی | استدلال استقرایی | درک شفاهی | درک کتبی | حساسیت به مسئله | تجسم | وضوح گفتار | بینایی نزدیک | اصالت | ترتیب‌دهی اطلاعات | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | بینایی دور | انعطاف‌پذیری بستار | استدلال ریاضی | توجه انتخابی | سرعت بستار | توانایی عددی</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>متخصصان بازآفرینی و بهسازی اراضی شهری | مدیران ارشد پایداری و توسعه پایدار | کاردان‌ها و تکنسین‌های مهندسی عمران | مهندسان عمران | تحلیل‌گران سیاست‌گذاری تغییرات اقلیمی | کارشناسان و متخصصان علوم محیط زیست و بهداشت محیط | سرپرستان رده‌اول اپراتورهای ماشین‌آلات جابه‌جایی بار و وسایل نقلیه | متصدیان حمل‌ونقل کالا و فورواردرها | تکنسین‌های هیدرولوژی و آب‌شناسی | بوم‌شناسان صنعتی | متخصصان لجستیک و زنجیره تأمین | تحلیل‌گران لجستیک | مهندسان لجستیک | تحلیل‌گران مدیریت و فرایندها | کارشناسان مدیریت پروژه | کارشناسان پایداری محیطی | تکنسین‌های ترافیک | مهندسان حمل‌ونقل | مدیران حمل‌ونقل، انبارداری و توزیع | برنامه‌ریزان شهری و منطقه‌ای</t>
+          <t>مدیران و کارشناسان احیا و بازسازی اراضی قهوه‌ای و آلوده | مدیران ارشد پایداری سازمانی | کارشناسان و تکنسین‌های مهندسی عمران | مهندسان عمران | تحلیل‌گران خط‌مشی تغییر اقلیم | کارشناسان و متخصصان علوم محیطی (شامل بهداشت) | سرپرستان رده‌اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابه‌جایی بار | کارشناسان و متصدیان فورواردری و حمل‌ونقل بین‌المللی کالا | تکنسین‌های آب‌شناسی و هیدرولوژی | بوم‌شناسان صنعتی | کارشناسان لجستیک و مدیریت زنجیره تأمین | تحلیل‌گران لجستیک و فرایند توزیع | مهندسان لجستیک و زنجیره تأمین | کارشناسان تحلیل مدیریت و روش‌ها | کارشناسان مدیریت پروژه | کارشناسان پایداری و توسعه پایدار | تکنسین‌های ترافیک | مهندسان حمل‌ونقل و ترافیک | مدیران حمل‌ونقل، انبارداری و توزیع | برنامه‌ریزان شهری و منطقه‌ای</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | شنیدن فعال | نگارش | یادگیری فعال | نظارت | سخن گفتن</t>
+          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | نگارش | یادگیری فعال | نظارت | سخن گفتن</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>تولید و فرآوری مواد غذایی | زیست‌شناسی | شیمی | مکانیک | ریاضیات | مدیریت و امور اداری</t>
+          <t>تولید مواد غذایی | زیست‌شناسی | شیمی | مکانیک | ریاضیات | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | دید نزدیک | درک کتبی | استدلال قیاسی | بیان کتبی | استدلال استقرایی | مرتب‌سازی اطلاعات | ثبات دست و بازو | تشخیص رنگ‌ها | انعطاف‌پذیری در دسته‌بندی | سرعت کار با اعداد | استدلال ریاضی | ابتکار و اصالت | روانی و سیالی ایده‌ها | وضوح گفتار | تشخیص گفتار | دید دور | دقت کنترل ابزار | توجه انتخابی | سرعت ادراک | انعطاف‌پذیری در تحلیل الگوها</t>
+          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | بینایی نزدیک | درک کتبی | استدلال قیاسی | بیان کتبی | استدلال استقرایی | ترتیب‌دهی اطلاعات | ثبات دست و بازو | تشخیص رنگ بصری | انعطاف‌پذیری دسته‌بندی | توانایی عددی | استدلال ریاضی | اصالت | روانی ایده‌ها | وضوح گفتار | تشخیص گفتار | بینایی دور | دقت کنترل | توجه انتخابی | سرعت ادراکی | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>مهندسان کشاورزی | استادان علوم کشاورزی دانشگاه | متخصصان علوم دامی | تکنسین‌های فرآوری سوخت‌های زیستی | مدیران تولید سوخت‌های زیستی | تکنسین‌های علوم زیستی | تکنسین‌های شیمی | شیمی‌دانان | کاردان‌ها و تکنسین‌های مهندسی محیط زیست | تکنسین‌های علوم محیط زیست و بهداشت محیط | مدیران مزارع، دامداری‌ها و واحدهای کشاورزی | کارگران زراعت، باغبانی و گلخانه | سرپرستان رده‌اول کارگران کشاورزی، شیلات و جنگلداری | تکنسین‌های صنایع غذایی | متخصصان و دانشمندان صنایع غذایی | تکنسین‌های جنگلداری و حفاظت منابع طبیعی | تکنسین‌های آزمایشگاه تشخیص طبی و بالینی | میکروبیولوژیست‌ها | تکنسین‌های کشاورزی دقیق | متخصصان علوم خاک و گیاه‌شناسی</t>
+          <t>مهندسان کشاورزی | استادان و مدرسان علوم کشاورزی در دانشگاه‌ها و مراکز آموزش عالی | متخصصان علوم دامی | تکنسین‌های فراوری سوخت‌های زیستی | مدیران تولید سوخت‌های زیستی | تکنسین‌های علوم زیستی | تکنسین‌های شیمی | شیمی‌دانان | کارشناسان و تکنسین‌های مهندسی محیط زیست | تکنسین‌های علوم و بهداشت محیط زیست | مدیران امور کشاورزی، دامپروری و شیلات | کارگران زراعت، نهالستان و گلخانه | سرپرستان رده‌اول کارگران کشاورزی، شیلات و جنگل‌داری | تکنسین‌های علوم و صنایع غذایی | متخصصان و کارشناسان علوم و صنایع غذایی | کاردان‌ها و تکنسین‌های جنگل‌داری و حفاظت منابع طبیعی | کاردان‌های آزمایشگاه‌های پزشکی و بالینی | میکروبیولوژیست‌ها | تکنسین‌های کشاورزی دقیق | متخصصان خاک‌شناسی و علوم گیاهی</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | سخن گفتن | تفکر انتقادی | نگارش | یادگیری فعال | ریاضیات | نظارت | راهبردهای یادگیری</t>
+          <t>درک مطلب | گوش دادن فعال | سخن گفتن | تفکر انتقادی | نگارش | یادگیری فعال | ریاضیات | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | رایانه و الکترونیک | فروش و بازاریابی | زبان انگلیسی | ریاضیات | مهندسی و فناوری | زیست‌شناسی | تولید و فرآوری مواد غذایی | مکانیک | جغرافیا | آموزش و تدریس | شیمی | تولید و فراوری صنعتی</t>
+          <t>خدمات مشتری و شخصی | رایانه و الکترونیک | فروش و بازاریابی | زبان انگلیسی | ریاضیات | مهندسی و فناوری | زیست‌شناسی | تولید مواد غذایی | مکانیک | جغرافیا | آموزش و پرورش | شیمی | تولید و فرآوری</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>استدلال قیاسی | استدلال استقرایی | درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | دید نزدیک | مرتب‌سازی اطلاعات | حساسیت به مسئله | وضوح گفتار | سرعت ادراک | انعطاف‌پذیری در تحلیل الگوها | استدلال ریاضی | انعطاف‌پذیری در دسته‌بندی | روانی و سیالی ایده‌ها | ابتکار و اصالت | چابکی دستی | ثبات دست و بازو | دقت کنترل ابزار | توجه انتخابی | تجسم و تصویرسازی ذهنی | سرعت درک الگوها | سرعت کار با اعداد | دید دور | تشخیص گفتار</t>
+          <t>استدلال قیاسی | استدلال استقرایی | درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | بینایی نزدیک | ترتیب‌دهی اطلاعات | حساسیت به مسئله | وضوح گفتار | سرعت ادراکی | انعطاف‌پذیری بستار | استدلال ریاضی | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | مهارت دستی | ثبات دست و بازو | دقت کنترل | توجه انتخابی | تجسم | سرعت بستار | توانایی عددی | بینایی دور | تشخیص گفتار</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>مهندسان کشاورزی | تکنسین‌های کشاورزی | دانشمندان و کارشناسان حفاظت محیط زیست | دانشمندان داده | کاردان‌ها و تکنسین‌های مهندسی محیط زیست | تکنسین‌های علوم محیط زیست و بهداشت محیط | کارشناسان و متخصصان علوم محیط زیست و بهداشت محیط | مدیران مزارع، دامداری‌ها و واحدهای کشاورزی | کارگران زراعت، باغبانی و گلخانه | متخصصان و دانشمندان صنایع غذایی | تکنسین‌های جنگلداری و حفاظت منابع طبیعی | تکنسین‌های زمین‌شناسی، به‌جز تکنسین‌های هیدرولوژی | تکنسین‌های هیدرولوژی و آب‌شناسی | بوم‌شناسان صنعتی | کاردان‌ها و تکنسین‌های مهندسی صنایع | مهندسان صنایع | مدیران مراتع و مرتع‌داران | متخصصان و پژوهشگران سنجش از دور | تکنسین‌های سنجش از دور | متخصصان علوم خاک و گیاه‌شناسی</t>
+          <t>مهندسان کشاورزی | تکنسین‌های کشاورزی | دانشمندان حفاظت از منابع طبیعی | دانشمندان داده | کارشناسان و تکنسین‌های مهندسی محیط زیست | تکنسین‌های علوم و بهداشت محیط زیست | کارشناسان و متخصصان علوم محیطی (شامل بهداشت) | مدیران امور کشاورزی، دامپروری و شیلات | کارگران زراعت، نهالستان و گلخانه | متخصصان و کارشناسان علوم و صنایع غذایی | کاردان‌ها و تکنسین‌های جنگل‌داری و حفاظت منابع طبیعی | کاردان‌ها و تکنسین‌های زمین‌شناسی به‌جز آب‌زمین‌شناسی | تکنسین‌های آب‌شناسی و هیدرولوژی | بوم‌شناسان صنعتی | کارشناسان و تکنسین‌های مهندسی صنایع | مهندسان صنایع | مدیران و کارشناسان مدیریت مراتع | دانشمندان و فناوران سنجش از دور | تکنسین‌های سنجش از دور | متخصصان خاک‌شناسی و علوم گیاهی</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | نگارش | سخن گفتن | تفکر انتقادی | مهارت‌های علمی و آزمایشگاهی | نظارت | یادگیری فعال</t>
+          <t>درک مطلب | گوش دادن فعال | نگارش | سخن گفتن | تفکر انتقادی | علوم | نظارت | یادگیری فعال</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>تولید و فرآوری مواد غذایی | تولید و فراوری صنعتی | شیمی | زبان انگلیسی | رایانه و الکترونیک | زیست‌شناسی | ریاضیات</t>
+          <t>تولید مواد غذایی | تولید و فرآوری | شیمی | زبان انگلیسی | رایانه و الکترونیک | زیست‌شناسی | ریاضیات</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>دید نزدیک | درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | تشخیص رنگ‌ها | تشخیص گفتار | وضوح گفتار | توجه انتخابی | انعطاف‌پذیری در دسته‌بندی | مرتب‌سازی اطلاعات | سرعت ادراک | انعطاف‌پذیری در تحلیل الگوها | سرعت کار با اعداد | استدلال ریاضی</t>
+          <t>بینایی نزدیک | درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | تشخیص رنگ بصری | تشخیص گفتار | وضوح گفتار | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | سرعت ادراکی | انعطاف‌پذیری بستار | توانایی عددی | استدلال ریاضی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>بازرسان محصولات کشاورزی و دامی | تکنسین‌های کشاورزی | متخصصان علوم دامی | تکنسین‌های فرآوری سوخت‌های زیستی | تکنسین‌های علوم زیستی | کاردان‌ها و تکنسین‌های کالیبراسیون و ابزار دقیق | تکنسین‌های شیمی | شیمی‌دانان | متصدیان فرمولاسیون و ترکیب مواد غذایی | متخصصان و دانشمندان صنایع غذایی | اپراتورهای ماشین‌آلات پخت، برشته‌کاری و خشک‌کردن مواد غذایی و دخانیات | درجه‌بندی‌کنندگان و سورت‌کنندگان محصولات کشاورزی | کاردان‌ها و تکنسین‌های مهندسی صنایع | بازرسان، نمونه‌برداران و آزمون‌گران کنترل کیفیت کالا | تکنسین‌های آزمایشگاه تشخیص طبی و بالینی | کارشناسان آزمایشگاه تشخیص طبی و بالینی | میکروبیولوژیست‌ها | تحلیل‌گران کنترل کیفیت فرایند | مدیران سیستم‌های کنترل کیفیت | اپراتورها و تنظیم‌کنندگان دستگاه‌های جداسازی، فیلتراسیون، تقطیر و تصفیه</t>
+          <t>بازرسان محصولات و فرآورده‌های کشاورزی | تکنسین‌های کشاورزی | متخصصان علوم دامی | تکنسین‌های فراوری سوخت‌های زیستی | تکنسین‌های علوم زیستی | تکنسین‌ها و کارشناسان فنی کالیبراسیون | تکنسین‌های شیمی | شیمی‌دانان | تولیدکنندگان فرمولی و دسته‌ای مواد غذایی | متخصصان و کارشناسان علوم و صنایع غذایی | اپراتورهای ماشین‌آلات برشته‌کاری، پخت و خشک‌کن مواد غذایی و توتون | کارگران درجه‌بندی و تفکیک محصولات کشاورزی | کارشناسان و تکنسین‌های مهندسی صنایع | بازرسان، آزمونگران، تفکیک‌کنندگان، نمونه‌برداران و توزین‌گران | کاردان‌های آزمایشگاه‌های پزشکی و بالینی | کارشناسان علوم آزمایشگاهی بالینی | میکروبیولوژیست‌ها | کارشناسان تحلیل کنترل کیفیت | مدیران سیستم‌های کنترل کیفیت | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات جداسازی، فیلتراسیون، شفاف‌سازی، ترسیب و تقطیر</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | مهارت‌های علمی و آزمایشگاهی | شنیدن فعال | یادگیری فعال | نگارش | سخن گفتن | نظارت | ریاضیات</t>
+          <t>درک مطلب | تفکر انتقادی | علوم | گوش دادن فعال | یادگیری فعال | نگارش | سخن گفتن | نظارت | ریاضیات</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -917,7 +917,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>دید نزدیک | درک شفاهی | استدلال استقرایی | بیان شفاهی | مرتب‌سازی اطلاعات | بیان کتبی | استدلال قیاسی | درک کتبی | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری در دسته‌بندی | حساسیت به مسئله | توجه انتخابی | انعطاف‌پذیری در تحلیل الگوها | استدلال ریاضی | روانی و سیالی ایده‌ها | تشخیص رنگ‌ها | چابکی انگشتان | ثبات دست و بازو | سرعت ادراک | سرعت کار با اعداد | تجسم و تصویرسازی ذهنی</t>
+          <t>بینایی نزدیک | درک شفاهی | استدلال استقرایی | بیان شفاهی | ترتیب‌دهی اطلاعات | بیان کتبی | استدلال قیاسی | درک کتبی | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | حساسیت به مسئله | توجه انتخابی | انعطاف‌پذیری بستار | استدلال ریاضی | روانی ایده‌ها | تشخیص رنگ بصری | مهارت انگشتان | ثبات دست و بازو | سرعت ادراکی | توانایی عددی | تجسم</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>تکنسین‌های کشاورزی | بیوشیمی‌دانان و بیوفیزیک‌دانان | مهندسان زیستی و مهندسان پزشکی | متخصصان و پژوهشگران بیوانفورماتیک | تکنسین‌های بیوانفورماتیک | استادان علوم زیستی دانشگاه | زیست‌شناسان | کاردان‌ها و تکنسین‌های کالیبراسیون و ابزار دقیق | تکنسین‌های شیمی | شیمی‌دانان | تکنسین‌های سیتوژنتیک | متخصصان ژنتیک | تکنسین‌های بافت‌شناسی و آزمایشگاه پاتولوژی | کارشناسان و بافت‌شناسان آزمایشگاهی | تکنسین‌های آزمایشگاه تشخیص طبی و بالینی | کارشناسان آزمایشگاه تشخیص طبی و بالینی | میکروبیولوژیست‌ها | زیست‌شناسان سلولی و مولکولی | کاردان‌ها و تکنسین‌های مهندسی نانوفناوری | مدیران علوم پایه و تجربی</t>
+          <t>تکنسین‌های کشاورزی | زیست‌شیمی‌دانان و زیست‌فیزیک‌دانان | مهندسان پزشکی و بیوانجینیرینگ | متخصصان بیوانفورماتیک | تکنسین‌های بیوانفورماتیک | استادان و مدرسان علوم زیستی در دانشگاه‌ها و مراکز آموزش عالی | زیست‌شناسان | تکنسین‌ها و کارشناسان فنی کالیبراسیون | تکنسین‌های شیمی | شیمی‌دانان | کارشناسان سیتوژنتیک | متخصصان ژنتیک | کاردان‌های پاتولوژی و بافت‌شناسی | هیستوتکنولوژیست‌ها / کارشناسان بافت‌شناسی | کاردان‌های آزمایشگاه‌های پزشکی و بالینی | کارشناسان علوم آزمایشگاهی بالینی | میکروبیولوژیست‌ها | زیست‌شناسان سلولی و مولکولی | کارشناسان و تکنسین‌های مهندسی نانوتکنولوژی | مدیران علوم طبیعی و پایه‌ای</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>مهارت‌های علمی و آزمایشگاهی | تفکر انتقادی | درک مطلب | شنیدن فعال | نگارش | نظارت | سخن گفتن | یادگیری فعال | راهبردهای یادگیری | ریاضیات</t>
+          <t>علوم | تفکر انتقادی | درک مطلب | گوش دادن فعال | نگارش | نظارت | سخن گفتن | یادگیری فعال | راهبردهای یادگیری | ریاضیات</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>دید نزدیک | درک کتبی | بیان کتبی | درک شفاهی | حساسیت به مسئله | استدلال استقرایی | مرتب‌سازی اطلاعات | بیان شفاهی | استدلال قیاسی | انعطاف‌پذیری در دسته‌بندی | وضوح گفتار | تشخیص گفتار | دقت کنترل ابزار | تجسم و تصویرسازی ذهنی | انعطاف‌پذیری در تحلیل الگوها | استدلال ریاضی | چابکی انگشتان | چابکی دستی | ثبات دست و بازو | توجه انتخابی | روانی و سیالی ایده‌ها | سرعت ادراک | سرعت درک الگوها | سرعت کار با اعداد | ابتکار و اصالت | تشخیص رنگ‌ها</t>
+          <t>بینایی نزدیک | درک کتبی | بیان کتبی | درک شفاهی | حساسیت به مسئله | استدلال استقرایی | ترتیب‌دهی اطلاعات | بیان شفاهی | استدلال قیاسی | انعطاف‌پذیری دسته‌بندی | وضوح گفتار | تشخیص گفتار | دقت کنترل | تجسم | انعطاف‌پذیری بستار | استدلال ریاضی | مهارت انگشتان | مهارت دستی | ثبات دست و بازو | توجه انتخابی | روانی ایده‌ها | سرعت ادراکی | سرعت بستار | توانایی عددی | اصالت | تشخیص رنگ بصری</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>کاردان‌ها و تکنسین‌های مهندسی هوافضا و عملیات پرواز | تکنسین‌های کشاورزی | تکنسین‌های علوم زیستی | کاردان‌ها و تکنسین‌های کالیبراسیون و ابزار دقیق | مهندسان شیمی | اپراتورها و متصدیان تجهیزات شیمیایی | اپراتورها و متصدیان سیستم‌ها و واحدهای صنایع شیمیایی | شیمی‌دانان | تکنسین‌های علوم محیط زیست و بهداشت محیط | تکنسین‌های صنایع غذایی | کاردان‌ها و تکنسین‌های مهندسی صنایع | مهندسان صنایع | بازرسان، نمونه‌برداران و آزمون‌گران کنترل کیفیت کالا | مهندسان مواد و متالورژی | دانشمندان و متخصصان علم مواد | کاردان‌ها و تکنسین‌های مهندسی مکانیک | تکنسین‌های آزمایشگاه تشخیص طبی و بالینی | کارشناسان آزمایشگاه تشخیص طبی و بالینی | کاردان‌ها و تکنسین‌های مهندسی نانوفناوری | تحلیل‌گران کنترل کیفیت فرایند</t>
+          <t>کارشناسان و تکنسین‌های مهندسی و عملیات هوافضا | تکنسین‌های کشاورزی | تکنسین‌های علوم زیستی | تکنسین‌ها و کارشناسان فنی کالیبراسیون | مهندسان شیمی | اپراتورها و متصدیان ماشین‌آلات و راکتورهای شیمیایی | اپراتورهای تأسیسات و سیستم‌های فرایندی صنایع شیمیایی | شیمی‌دانان | تکنسین‌های علوم و بهداشت محیط زیست | تکنسین‌های علوم و صنایع غذایی | کارشناسان و تکنسین‌های مهندسی صنایع | مهندسان صنایع | بازرسان، آزمونگران، تفکیک‌کنندگان، نمونه‌برداران و توزین‌گران | مهندسان متالورژی و مواد | کارشناسان و دانشمندان علوم مواد | کارشناسان و تکنسین‌های مهندسی مکانیک | کاردان‌های آزمایشگاه‌های پزشکی و بالینی | کارشناسان علوم آزمایشگاهی بالینی | کارشناسان و تکنسین‌های مهندسی نانوتکنولوژی | کارشناسان تحلیل کنترل کیفیت</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | نگارش | سخن گفتن | تفکر انتقادی | نظارت | مهارت‌های علمی و آزمایشگاهی | ریاضیات | یادگیری فعال | راهبردهای یادگیری</t>
+          <t>درک مطلب | گوش دادن فعال | نگارش | سخن گفتن | تفکر انتقادی | نظارت | علوم | ریاضیات | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | شیمی | زیست‌شناسی | حقوق و امور دولتی | رایانه و الکترونیک | ریاضیات | ایمنی و امنیت عمومی | مهندسی و فناوری</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | شیمی | زیست‌شناسی | قانون و دولت | رایانه و الکترونیک | ریاضیات | ایمنی و امنیت عمومی | مهندسی و فناوری</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | دید نزدیک | بیان کتبی | استدلال قیاسی | استدلال استقرایی | وضوح گفتار | حساسیت به مسئله | تشخیص گفتار | مرتب‌سازی اطلاعات | انعطاف‌پذیری در دسته‌بندی | انعطاف‌پذیری در تحلیل الگوها | سرعت کار با اعداد | استدلال ریاضی | روانی و سیالی ایده‌ها | دید دور | ثبات دست و بازو | توجه انتخابی | تجسم و تصویرسازی ذهنی | سرعت ادراک</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بینایی نزدیک | بیان کتبی | استدلال قیاسی | استدلال استقرایی | وضوح گفتار | حساسیت به مسئله | تشخیص گفتار | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار | توانایی عددی | استدلال ریاضی | روانی ایده‌ها | بینایی دور | ثبات دست و بازو | توجه انتخابی | تجسم | سرعت ادراکی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>تکنسین‌های علوم زیستی | متخصصان بازآفرینی و بهسازی اراضی شهری | تکنسین‌های شیمی | دانشمندان و کارشناسان حفاظت محیط زیست | بازرسان انطباق و نظارت زیست‌محیطی | کاردان‌ها و تکنسین‌های مهندسی محیط زیست | مهندسان محیط زیست | کارشناسان و متخصصان علوم محیط زیست و بهداشت محیط | تکنسین‌های زمین‌شناسی، به‌جز تکنسین‌های هیدرولوژی | کارگران جمع‌آوری و امحای مواد زائد خطرناک | مهندسان بهداشت و ایمنی صنعتی، به‌جز مهندسان و بازرسان ایمنی معدن | تکنسین‌های هیدرولوژی و آب‌شناسی | هیدرولوژیست‌ها و آب‌شناسان | بوم‌شناسان صنعتی | مهندسان هسته‌ای | تکنسین‌های پایش و حفاظت پرتوی هسته‌ای | کارشناسان بهداشت حرفه‌ای و ایمنی کار | کارشناسان و متخصصان منابع آب | اپراتورها و متصدیان تصفیه‌خانه‌های آب و فاضلاب صنعتی و شهری | مهندسان آب و فاضلاب</t>
+          <t>تکنسین‌های علوم زیستی | مدیران و کارشناسان احیا و بازسازی اراضی قهوه‌ای و آلوده | تکنسین‌های شیمی | دانشمندان حفاظت از منابع طبیعی | بازرسان رعایت ضوابط زیست‌محیطی | کارشناسان و تکنسین‌های مهندسی محیط زیست | مهندسان محیط‌زیست | کارشناسان و متخصصان علوم محیطی (شامل بهداشت) | کاردان‌ها و تکنسین‌های زمین‌شناسی به‌جز آب‌زمین‌شناسی | کارگران امحا و پاک‌سازی مواد خطرناک | مهندسان بهداشت و ایمنی، به‌جز مهندسان و بازرسان ایمنی معدن | تکنسین‌های آب‌شناسی و هیدرولوژی | آب‌شناسان و هیدرولوژیست‌ها | بوم‌شناسان صنعتی | مهندسان هسته‌ای | تکنسین‌های پایش و حفاظت پرتوی | کارشناسان بهداشت حرفه‌ای و ایمنی کار | کارشناسان و متخصصان مدیریت منابع آب | اپراتورهای تصفیه‌خانه و شبکه‌های انتقال آب و فاضلاب | مهندسان آب و فاضلاب</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
